--- a/tasks/finalpool/terminal-howtocook-gform-excel-notion-email/groundtruth_workspace/Meal_Program_Plan.xlsx
+++ b/tasks/finalpool/terminal-howtocook-gform-excel-notion-email/groundtruth_workspace/Meal_Program_Plan.xlsx
@@ -477,7 +477,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>checkbox</t>
+          <t>multiple_choice</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>scale</t>
+          <t>short_text</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cola Chicken Wings</t>
+          <t>可乐鸡翅</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Meat</t>
+          <t>荤菜</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -560,12 +560,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sweet and Sour Pork</t>
+          <t>咕噜肉</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Meat</t>
+          <t>荤菜</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -575,12 +575,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cold Cucumber Salad</t>
+          <t>凉拌黄瓜</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vegetable</t>
+          <t>素菜</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -590,12 +590,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Stir-fried Vegetables</t>
+          <t>地三鲜</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vegetable</t>
+          <t>素菜</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -605,27 +605,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Fried Noodles</t>
+          <t>炒河粉</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Staple</t>
+          <t>主食</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cream Mushroom Soup</t>
+          <t>奶油蘑菇汤</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Soup</t>
+          <t>汤</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -635,16 +635,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Steamed Fish</t>
+          <t>红烧鱼</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Seafood</t>
+          <t>水产</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -686,7 +686,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cola Chicken Wings</t>
+          <t>可乐鸡翅</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cold Cucumber Salad</t>
+          <t>凉拌黄瓜</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -716,7 +716,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Steamed Fish</t>
+          <t>红烧鱼</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fried Noodles</t>
+          <t>炒河粉</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -746,7 +746,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cream Mushroom Soup</t>
+          <t>奶油蘑菇汤</t>
         </is>
       </c>
       <c r="C6" t="n">
